--- a/Result/profitability/5525.xlsx
+++ b/Result/profitability/5525.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5462499999999999</v>
+        <v>0.665</v>
       </c>
       <c r="N2" t="n">
-        <v>37.97875</v>
+        <v>38.785</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.91</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61125</v>
+        <v>0.6674999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>37.05375</v>
+        <v>37.7375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5225</v>
+        <v>0.705</v>
       </c>
       <c r="N4" t="n">
-        <v>36.67874999999999</v>
+        <v>34.805</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5712499999999999</v>
+        <v>0.7437499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>33.38625</v>
+        <v>32.7025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.61375</v>
+        <v>0.7912499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>34.155</v>
+        <v>32.21625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.63625</v>
+        <v>0.6</v>
       </c>
       <c r="N7" t="n">
-        <v>31.14375</v>
+        <v>30.7425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.455</v>
+        <v>0.4974999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>29.8275</v>
+        <v>30.065</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.37</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3549999999999999</v>
+        <v>0.355</v>
       </c>
       <c r="N12" t="n">
         <v>26.95</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E75" t="n">
+        <v>757</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>599</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>27.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>592</v>
+      </c>
+      <c r="K75" t="n">
+        <v>411</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05803298717165539</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-34.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.469999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1363749688357018</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
